--- a/data/nest_issues_commented/MP_nest_data_issues_220825.xlsx
+++ b/data/nest_issues_commented/MP_nest_data_issues_220825.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">signaccess,ropefence</t>
   </si>
   <si>
-    <t xml:space="preserve">Nest habitat is not beach, dune, foredune/face, estuary/spit, or rocks; </t>
+    <t xml:space="preserve">Nest habitat is not beach, dune, foredune/face, or estuary/spit; </t>
   </si>
   <si>
     <t xml:space="preserve">201213</t>

--- a/data/nest_issues_commented/MP_nest_data_issues_220825.xlsx
+++ b/data/nest_issues_commented/MP_nest_data_issues_220825.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <t xml:space="preserve">season</t>
   </si>
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Gunnamatta SLSC Far East (P1)</t>
   </si>
   <si>
-    <t xml:space="preserve">201112_Gunnamatta Pair 1_1</t>
+    <t xml:space="preserve">201112_Gunnamatta SLSC Far East (P1)_1</t>
   </si>
   <si>
     <t xml:space="preserve">05102011</t>
@@ -153,364 +153,346 @@
     <t xml:space="preserve">Management type is not sufficient for making levels; </t>
   </si>
   <si>
+    <t xml:space="preserve">201314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koonya East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Koonya East_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11112013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18112013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaccess,ropefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nest habitat is not beach, dune, foredune/face, or estuary/spit; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koonya West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Koonya West_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30012013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13022013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">permanentfence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunnamatta Car Park 1 (P6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Gunnamatta Car Park 1 (P6)_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17122011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12012012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaccess,signnest,ropefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-38.444824300000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.8551381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Gunnamatta Car Park 1 (P6)_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04022011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Gunnamatta SLSC Far East (P1)_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22102010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25112010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/3 adult size, fluffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heyfield Pair 2 (east side) Rye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Heyfield Pair 2 (east side) Rye_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19122010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22122010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Heyfield Pair 2 (east side) Rye_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Koonya West_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt Nepean Observatory Pt - The Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Pt Nepean Observatory Pt - The Steps_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03022011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Pt Nepean Observatory Pt - The Steps_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05022011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heyfield Pair 1 (west side) Rye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Heyfield Pair 1 (west side) Rye_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03102009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18102009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ropefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montforts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Montforts_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26112009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07122009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Montforts_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03012010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04022010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rye car park east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Rye car park east_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13022010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Andrews - Miami Drive West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_St Andrews - Miami Drive West_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20012010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08022010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signnest,ropefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Andrews carpark west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_St Andrews carpark west_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23102009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02112009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alison Ave, Rye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Alison Ave, Rye_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15122008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08012009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunnamatta Fingal Tk East (P5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Gunnamatta Fingal Tk East (P5)_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21102008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13112008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunnamatta Fingal Tk West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Gunnamatta Fingal Tk West_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09012009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06022009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Gunnamatta Fingal Tk West_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20022009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Gunnamatta SLSC Far East (P1)_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07012009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10022009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miami drive east access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Miami drive east access_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16102008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17102008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Pt Nepean Observatory Pt - The Steps_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15012009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Andrews Boags Rocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_St Andrews Boags Rocks_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24112008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08122008</t>
+  </si>
+  <si>
     <t xml:space="preserve">200708</t>
   </si>
   <si>
-    <t xml:space="preserve">Moana crt access (east edge)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200708_St Andrews Moana access (east edge)_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14012008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09022008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ringlockfence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/3 adult size, fluffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koonya East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201314_Koonya East_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11112013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18112013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not specified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signaccess,ropefence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nest habitat is not beach, dune, foredune/face, or estuary/spit; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">201213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koonya West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201213_Koonya West_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30012013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13022013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">permanentfence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunnamatta Car Park 1 (P6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201112_Gunnamatta Pair 6_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17122011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12012012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signaccess,signnest,ropefence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-38.444824300000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.8551381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Gunnamatta Pair 6_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04022011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Gunnamatta 1st territory_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22102010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18112010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not found</t>
+    <t xml:space="preserve">200708_Pt Nepean Observatory Pt - The Steps_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15112007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12122007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adult size, mottled grey</t>
   </si>
   <si>
     <t xml:space="preserve">27</t>
   </si>
   <si>
-    <t xml:space="preserve">Heyfield Pair 2 (east side) Rye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Number 16 Rye_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19122010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22122010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Number 16 Rye_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Koonya West_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt Nepean Observatory Pt - The Steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Point Nepean Observatory Point_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03022011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Point Nepean The Bend_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heyfield Pair 1 (west side) Rye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Heyfields Lizard Head pair_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03102009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11102009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ropefence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montforts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Montforts_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26112009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30112009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Montforts_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03012010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28012010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rye car park east</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Rye East_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06022010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St Andrews - Miami Drive West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_St Andrews - Miami Drive West_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20012010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01022010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signnest,ropefence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St Andrews carpark west</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_St Andrews Moana East_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23102009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02112009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alison Ave, Rye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Rye Alison Ave W_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15122008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08012009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunnamatta Fingal Tk East (P5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Fingal_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21102008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13112008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunnamatta Fingal Tk West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Gunnamatta 3rd territory_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09012009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06022009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Gunnamatta 3rd territory_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20022009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Gunnamatta 1st territory_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07012009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03022009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miami drive east access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Miami East_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16102008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17102008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Point Nepean Observatory Point_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15012009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10022009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St Andrews Boags Rocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_St Andrews Boags Rocks_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24112008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08122008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200708_Point Nepean Observatory Point_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15112007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05122007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adult size, mottled grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
     <t xml:space="preserve">200607</t>
   </si>
   <si>
     <t xml:space="preserve">Gunnamatta Fingal Tk (P4)</t>
   </si>
   <si>
-    <t xml:space="preserve">200607_Fingal_1</t>
+    <t xml:space="preserve">200607_Gunnamatta Fingal Tk (P4)_1</t>
   </si>
   <si>
     <t xml:space="preserve">01092006</t>
@@ -525,10 +507,7 @@
     <t xml:space="preserve">144 52.400</t>
   </si>
   <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200607_Number 16 Rye_1</t>
+    <t xml:space="preserve">200607_Heyfield Pair 2 (east side) Rye_1</t>
   </si>
   <si>
     <t xml:space="preserve">20092006</t>
@@ -1045,7 +1024,7 @@
       </c>
       <c r="AB2"/>
       <c r="AC2" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="AD2" t="s">
         <v>43</v>
@@ -1071,60 +1050,56 @@
         <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
         <v>52</v>
       </c>
       <c r="K3"/>
       <c r="L3"/>
-      <c r="M3" s="1" t="n">
-        <v>39490</v>
-      </c>
+      <c r="M3" s="1"/>
       <c r="N3" s="1" t="n">
-        <v>39452</v>
-      </c>
-      <c r="O3" t="s">
-        <v>53</v>
-      </c>
+        <v>41593</v>
+      </c>
+      <c r="O3"/>
       <c r="P3" s="1" t="n">
-        <v>39487</v>
+        <v>41589</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>39461</v>
+        <v>41589</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>39487</v>
+        <v>41596</v>
       </c>
       <c r="S3" t="n">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="T3" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="U3" t="n">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1135,87 +1110,87 @@
       <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3"/>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
       <c r="AC3" t="n">
-        <v>317</v>
+        <v>231</v>
       </c>
       <c r="AD3" t="s">
         <v>43</v>
       </c>
       <c r="AE3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" t="s">
         <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
       </c>
       <c r="G4" t="s">
         <v>37</v>
       </c>
       <c r="H4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" t="s">
         <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>61</v>
       </c>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="n">
-        <v>41593</v>
-      </c>
+      <c r="N4" s="1"/>
       <c r="O4"/>
       <c r="P4" s="1" t="n">
-        <v>41589</v>
+        <v>41304</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>41589</v>
+        <v>41304</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>41596</v>
+        <v>41318</v>
       </c>
       <c r="S4" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="T4" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="U4" t="n">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1224,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>231</v>
+        <v>348</v>
       </c>
       <c r="AD4" t="s">
         <v>43</v>
@@ -1236,74 +1211,78 @@
         <v>44</v>
       </c>
       <c r="AF4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
         <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
       </c>
       <c r="G5" t="s">
         <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5"/>
-      <c r="L5"/>
+        <v>65</v>
+      </c>
+      <c r="K5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5"/>
       <c r="P5" s="1" t="n">
-        <v>41304</v>
+        <v>40894</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>41304</v>
+        <v>40894</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>41318</v>
+        <v>40920</v>
       </c>
       <c r="S5" t="n">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="T5" t="n">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="U5" t="n">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1312,10 +1291,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>359</v>
+        <v>284</v>
       </c>
       <c r="AD5" t="s">
         <v>43</v>
@@ -1324,66 +1303,62 @@
         <v>44</v>
       </c>
       <c r="AF5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
         <v>69</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
         <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" t="s">
-        <v>72</v>
       </c>
       <c r="G6" t="s">
         <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
         <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" t="s">
-        <v>75</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6"/>
       <c r="P6" s="1" t="n">
-        <v>40894</v>
+        <v>40572</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>40894</v>
+        <v>40572</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>40920</v>
+        <v>40578</v>
       </c>
       <c r="S6" t="n">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="T6" t="n">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="U6" t="n">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
@@ -1407,7 +1382,7 @@
         <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="AD6" t="s">
         <v>43</v>
@@ -1416,71 +1391,77 @@
         <v>44</v>
       </c>
       <c r="AF6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="K7"/>
       <c r="L7"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7"/>
+      <c r="M7" s="1" t="n">
+        <v>40503</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>40472</v>
+      </c>
+      <c r="O7" t="s">
+        <v>76</v>
+      </c>
       <c r="P7" s="1" t="n">
-        <v>40572</v>
+        <v>40507</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>40572</v>
+        <v>40473</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>40578</v>
+        <v>40507</v>
       </c>
       <c r="S7" t="n">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="T7" t="n">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="U7" t="n">
-        <v>215</v>
+        <v>144</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1489,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>232</v>
@@ -1501,71 +1482,65 @@
         <v>43</v>
       </c>
       <c r="AE7" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AF7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
         <v>81</v>
       </c>
-      <c r="E8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" t="s">
-        <v>82</v>
-      </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J8" t="s">
         <v>26</v>
       </c>
       <c r="K8"/>
       <c r="L8"/>
-      <c r="M8" s="1" t="n">
-        <v>40503</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>40465</v>
-      </c>
-      <c r="O8" t="s">
-        <v>53</v>
-      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8"/>
       <c r="P8" s="1" t="n">
-        <v>40500</v>
+        <v>40531</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>40473</v>
+        <v>40531</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>40500</v>
+        <v>40534</v>
       </c>
       <c r="S8" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="T8" t="n">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="U8" t="n">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1595,42 +1570,42 @@
         <v>43</v>
       </c>
       <c r="AE8" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="K9"/>
       <c r="L9"/>
@@ -1638,31 +1613,31 @@
       <c r="N9" s="1"/>
       <c r="O9"/>
       <c r="P9" s="1" t="n">
-        <v>40531</v>
+        <v>40555</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>40531</v>
+        <v>40555</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>40534</v>
+        <v>40567</v>
       </c>
       <c r="S9" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="T9" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="U9" t="n">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1671,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
         <v>232</v>
@@ -1686,39 +1661,39 @@
         <v>44</v>
       </c>
       <c r="AF9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
         <v>85</v>
       </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
         <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="K10"/>
       <c r="L10"/>
@@ -1726,31 +1701,31 @@
       <c r="N10" s="1"/>
       <c r="O10"/>
       <c r="P10" s="1" t="n">
+        <v>40549</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>40549</v>
+      </c>
+      <c r="R10" s="1" t="n">
         <v>40555</v>
       </c>
-      <c r="Q10" s="1" t="n">
-        <v>40555</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>40567</v>
-      </c>
       <c r="S10" t="n">
+        <v>186</v>
+      </c>
+      <c r="T10" t="n">
+        <v>186</v>
+      </c>
+      <c r="U10" t="n">
         <v>192</v>
       </c>
-      <c r="T10" t="n">
-        <v>192</v>
-      </c>
-      <c r="U10" t="n">
-        <v>204</v>
-      </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1759,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>232</v>
@@ -1774,24 +1749,24 @@
         <v>44</v>
       </c>
       <c r="AF10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
         <v>90</v>
@@ -1800,10 +1775,10 @@
         <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J11" t="s">
         <v>26</v>
@@ -1814,22 +1789,22 @@
       <c r="N11" s="1"/>
       <c r="O11"/>
       <c r="P11" s="1" t="n">
-        <v>40549</v>
+        <v>40564</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>40549</v>
+        <v>40564</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>40555</v>
+        <v>40577</v>
       </c>
       <c r="S11" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="T11" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="U11" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1862,62 +1837,68 @@
         <v>44</v>
       </c>
       <c r="AF11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
         <v>26</v>
       </c>
       <c r="K12"/>
       <c r="L12"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12"/>
+      <c r="M12" s="1" t="n">
+        <v>40575</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>40544</v>
+      </c>
+      <c r="O12" t="s">
+        <v>76</v>
+      </c>
       <c r="P12" s="1" t="n">
-        <v>40564</v>
+        <v>40579</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>40564</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>40577</v>
+        <v>40579</v>
       </c>
       <c r="S12" t="n">
         <v>201</v>
       </c>
       <c r="T12" t="n">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="U12" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1947,71 +1928,71 @@
         <v>43</v>
       </c>
       <c r="AE12" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="AF12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" t="s">
         <v>98</v>
       </c>
-      <c r="D13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>78</v>
-      </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
         <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="K13"/>
       <c r="L13"/>
       <c r="M13" s="1" t="n">
-        <v>40575</v>
+        <v>40100</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>40537</v>
+        <v>40069</v>
       </c>
       <c r="O13" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>40572</v>
+        <v>40104</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>40564</v>
+        <v>40089</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>40572</v>
+        <v>40104</v>
       </c>
       <c r="S13" t="n">
-        <v>201</v>
+        <v>91</v>
       </c>
       <c r="T13" t="n">
-        <v>209</v>
+        <v>106</v>
       </c>
       <c r="U13" t="n">
-        <v>209</v>
+        <v>106</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2020,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2029,83 +2010,83 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="AD13" t="s">
         <v>43</v>
       </c>
       <c r="AE13" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="AF13" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
         <v>100</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>101</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>102</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>103</v>
       </c>
-      <c r="E14" t="s">
-        <v>104</v>
-      </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
         <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="K14"/>
       <c r="L14"/>
       <c r="M14" s="1" t="n">
-        <v>40100</v>
+        <v>40150</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>40062</v>
+        <v>40119</v>
       </c>
       <c r="O14" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>40097</v>
+        <v>40154</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>40089</v>
+        <v>40143</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>40097</v>
+        <v>40154</v>
       </c>
       <c r="S14" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="T14" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="U14" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2114,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2123,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>316</v>
@@ -2135,39 +2116,39 @@
         <v>43</v>
       </c>
       <c r="AE14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="AF14" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
         <v>100</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" t="s">
         <v>106</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>107</v>
       </c>
-      <c r="D15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" t="s">
-        <v>109</v>
-      </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" t="s">
         <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
         <v>26</v>
@@ -2175,31 +2156,31 @@
       <c r="K15"/>
       <c r="L15"/>
       <c r="M15" s="1" t="n">
-        <v>40150</v>
+        <v>40209</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>40112</v>
+        <v>40178</v>
       </c>
       <c r="O15" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>40147</v>
+        <v>40213</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>40143</v>
+        <v>40181</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>40147</v>
+        <v>40213</v>
       </c>
       <c r="S15" t="n">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="T15" t="n">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="U15" t="n">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2229,39 +2210,39 @@
         <v>43</v>
       </c>
       <c r="AE15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" t="s">
         <v>106</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>111</v>
       </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>113</v>
-      </c>
       <c r="F16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s">
         <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J16" t="s">
         <v>26</v>
@@ -2269,31 +2250,31 @@
       <c r="K16"/>
       <c r="L16"/>
       <c r="M16" s="1" t="n">
-        <v>40209</v>
+        <v>40218</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>40171</v>
+        <v>40187</v>
       </c>
       <c r="O16" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>40206</v>
+        <v>40222</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>40181</v>
+        <v>40187</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>40206</v>
+        <v>40222</v>
       </c>
       <c r="S16" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="T16" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="U16" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2323,80 +2304,80 @@
         <v>43</v>
       </c>
       <c r="AE16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF16" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" t="s">
         <v>115</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>116</v>
       </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>117</v>
-      </c>
       <c r="F17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
         <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I17" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="K17"/>
       <c r="L17"/>
       <c r="M17" s="1" t="n">
-        <v>40218</v>
+        <v>40213</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>40180</v>
+        <v>40182</v>
       </c>
       <c r="O17" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>40215</v>
+        <v>40217</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>40181</v>
+        <v>40198</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>40215</v>
+        <v>40217</v>
       </c>
       <c r="S17" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="T17" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="U17" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2405,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="n">
         <v>316</v>
@@ -2420,12 +2401,12 @@
         <v>118</v>
       </c>
       <c r="AF17" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
         <v>119</v>
@@ -2437,51 +2418,45 @@
         <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
         <v>122</v>
       </c>
       <c r="G18" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I18" t="s">
         <v>39</v>
       </c>
       <c r="J18" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="K18"/>
       <c r="L18"/>
-      <c r="M18" s="1" t="n">
-        <v>40213</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>40175</v>
-      </c>
-      <c r="O18" t="s">
-        <v>53</v>
-      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18"/>
       <c r="P18" s="1" t="n">
-        <v>40210</v>
+        <v>40109</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>40198</v>
+        <v>40109</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>40210</v>
+        <v>40119</v>
       </c>
       <c r="S18" t="n">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="T18" t="n">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="U18" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2511,74 +2486,76 @@
         <v>43</v>
       </c>
       <c r="AE18" t="s">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="AF18" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" t="s">
         <v>125</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>126</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" t="s">
         <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" t="s">
-        <v>128</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
       </c>
       <c r="H19" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I19" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J19" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
+      <c r="N19" s="1" t="n">
+        <v>39799</v>
+      </c>
       <c r="O19"/>
       <c r="P19" s="1" t="n">
-        <v>40109</v>
+        <v>39797</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>40109</v>
+        <v>39797</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>40119</v>
+        <v>39821</v>
       </c>
       <c r="S19" t="n">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="T19" t="n">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="U19" t="n">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2587,13 +2564,13 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>316</v>
+        <v>236</v>
       </c>
       <c r="AD19" t="s">
         <v>43</v>
@@ -2602,36 +2579,36 @@
         <v>44</v>
       </c>
       <c r="AF19" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
         <v>129</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>130</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" t="s">
         <v>131</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F20" t="s">
-        <v>133</v>
       </c>
       <c r="G20" t="s">
         <v>37</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2639,27 +2616,25 @@
       <c r="K20"/>
       <c r="L20"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1" t="n">
-        <v>39799</v>
-      </c>
+      <c r="N20" s="1"/>
       <c r="O20"/>
       <c r="P20" s="1" t="n">
-        <v>39797</v>
+        <v>39742</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>39797</v>
+        <v>39742</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>39821</v>
+        <v>39765</v>
       </c>
       <c r="S20" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="T20" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="U20" t="n">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2692,36 +2667,36 @@
         <v>44</v>
       </c>
       <c r="AF20" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" t="s">
         <v>134</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" t="s">
         <v>135</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>136</v>
-      </c>
-      <c r="F21" t="s">
-        <v>137</v>
       </c>
       <c r="G21" t="s">
         <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J21" t="s">
         <v>26</v>
@@ -2729,25 +2704,27 @@
       <c r="K21"/>
       <c r="L21"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+      <c r="N21" s="1" t="n">
+        <v>40118</v>
+      </c>
       <c r="O21"/>
       <c r="P21" s="1" t="n">
-        <v>39742</v>
+        <v>39822</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>39742</v>
+        <v>39822</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>39765</v>
+        <v>39850</v>
       </c>
       <c r="S21" t="n">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="T21" t="n">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="U21" t="n">
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2780,36 +2757,36 @@
         <v>44</v>
       </c>
       <c r="AF21" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G22" t="s">
         <v>37</v>
       </c>
       <c r="H22" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J22" t="s">
         <v>26</v>
@@ -2818,26 +2795,26 @@
       <c r="L22"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1" t="n">
-        <v>40118</v>
+        <v>40027</v>
       </c>
       <c r="O22"/>
       <c r="P22" s="1" t="n">
-        <v>39822</v>
+        <v>39850</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>39822</v>
+        <v>39850</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>39850</v>
+        <v>39864</v>
       </c>
       <c r="S22" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="T22" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="U22" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2870,73 +2847,77 @@
         <v>44</v>
       </c>
       <c r="AF22" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
         <v>138</v>
       </c>
-      <c r="C23" t="s">
-        <v>142</v>
-      </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J23" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="K23"/>
       <c r="L23"/>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1" t="n">
+        <v>39850</v>
+      </c>
       <c r="N23" s="1" t="n">
-        <v>40027</v>
-      </c>
-      <c r="O23"/>
+        <v>39819</v>
+      </c>
+      <c r="O23" t="s">
+        <v>76</v>
+      </c>
       <c r="P23" s="1" t="n">
-        <v>39850</v>
+        <v>39854</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>39850</v>
+        <v>39820</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>39864</v>
+        <v>39854</v>
       </c>
       <c r="S23" t="n">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="T23" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="U23" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2945,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC23" t="n">
         <v>236</v>
@@ -2957,80 +2938,74 @@
         <v>43</v>
       </c>
       <c r="AE23" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AF23" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" t="s">
         <v>144</v>
       </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F24" t="s">
-        <v>146</v>
-      </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I24" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J24" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="K24"/>
       <c r="L24"/>
-      <c r="M24" s="1" t="n">
-        <v>39850</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>39812</v>
-      </c>
-      <c r="O24" t="s">
-        <v>53</v>
-      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24"/>
       <c r="P24" s="1" t="n">
-        <v>39847</v>
+        <v>39737</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>39820</v>
+        <v>39737</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>39847</v>
+        <v>39738</v>
       </c>
       <c r="S24" t="n">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="T24" t="n">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="U24" t="n">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3039,10 +3014,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>236</v>
@@ -3051,74 +3026,76 @@
         <v>43</v>
       </c>
       <c r="AE24" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="AF24" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F25" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G25" t="s">
         <v>37</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J25" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="K25"/>
       <c r="L25"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
+      <c r="N25" s="1" t="n">
+        <v>39830</v>
+      </c>
       <c r="O25"/>
       <c r="P25" s="1" t="n">
-        <v>39737</v>
+        <v>39828</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>39737</v>
+        <v>39828</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>39738</v>
+        <v>39854</v>
       </c>
       <c r="S25" t="n">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="T25" t="n">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="U25" t="n">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3127,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="n">
         <v>236</v>
@@ -3142,73 +3119,71 @@
         <v>44</v>
       </c>
       <c r="AF25" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F26" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G26" t="s">
         <v>37</v>
       </c>
       <c r="H26" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I26" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="K26"/>
       <c r="L26"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1" t="n">
-        <v>39830</v>
-      </c>
+      <c r="N26" s="1"/>
       <c r="O26"/>
       <c r="P26" s="1" t="n">
-        <v>39828</v>
+        <v>39776</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>39828</v>
+        <v>39776</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>39854</v>
+        <v>39790</v>
       </c>
       <c r="S26" t="n">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="T26" t="n">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="U26" t="n">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3217,10 +3192,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>236</v>
@@ -3232,62 +3207,68 @@
         <v>44</v>
       </c>
       <c r="AF26" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" t="s">
         <v>154</v>
       </c>
-      <c r="C27" t="s">
-        <v>155</v>
-      </c>
-      <c r="D27" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" t="s">
-        <v>156</v>
-      </c>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G27" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I27" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J27" t="s">
         <v>26</v>
       </c>
       <c r="K27"/>
       <c r="L27"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27"/>
+      <c r="M27" s="1" t="n">
+        <v>39451</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>39393</v>
+      </c>
+      <c r="O27" t="s">
+        <v>155</v>
+      </c>
       <c r="P27" s="1" t="n">
-        <v>39776</v>
+        <v>39428</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>39776</v>
+        <v>39401</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>39790</v>
+        <v>39428</v>
       </c>
       <c r="S27" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="T27" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="U27" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3311,77 +3292,81 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>236</v>
+        <v>317</v>
       </c>
       <c r="AD27" t="s">
         <v>43</v>
       </c>
       <c r="AE27" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="AF27" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G28" t="s">
         <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I28" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J28" t="s">
         <v>26</v>
       </c>
-      <c r="K28"/>
-      <c r="L28"/>
+      <c r="K28" t="s">
+        <v>162</v>
+      </c>
+      <c r="L28" t="s">
+        <v>163</v>
+      </c>
       <c r="M28" s="1" t="n">
-        <v>39451</v>
+        <v>39000</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>39386</v>
+        <v>38846</v>
       </c>
       <c r="O28" t="s">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>39421</v>
+        <v>38881</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>39401</v>
+        <v>38846</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>39421</v>
+        <v>38881</v>
       </c>
       <c r="S28" t="n">
-        <v>134</v>
+        <v>309</v>
       </c>
       <c r="T28" t="n">
-        <v>154</v>
+        <v>344</v>
       </c>
       <c r="U28" t="n">
-        <v>154</v>
+        <v>344</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3405,81 +3390,71 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="AD28" t="s">
         <v>43</v>
       </c>
       <c r="AE28" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="AF28" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
         <v>164</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>165</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" t="s">
         <v>166</v>
       </c>
-      <c r="E29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F29" t="s">
-        <v>167</v>
-      </c>
       <c r="G29" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I29" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J29" t="s">
         <v>26</v>
       </c>
-      <c r="K29" t="s">
-        <v>168</v>
-      </c>
-      <c r="L29" t="s">
-        <v>169</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>39000</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>38846</v>
-      </c>
-      <c r="O29" t="s">
-        <v>53</v>
-      </c>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29"/>
       <c r="P29" s="1" t="n">
-        <v>38881</v>
+        <v>38980</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>38846</v>
+        <v>38980</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>38881</v>
+        <v>38984</v>
       </c>
       <c r="S29" t="n">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="T29" t="n">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="U29" t="n">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -3509,98 +3484,10 @@
         <v>43</v>
       </c>
       <c r="AE29" t="s">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="AF29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>163</v>
-      </c>
-      <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" t="s">
-        <v>172</v>
-      </c>
-      <c r="F30" t="s">
-        <v>173</v>
-      </c>
-      <c r="G30" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" t="s">
-        <v>60</v>
-      </c>
-      <c r="I30" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30"/>
-      <c r="P30" s="1" t="n">
-        <v>38980</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>38980</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>38984</v>
-      </c>
-      <c r="S30" t="n">
-        <v>78</v>
-      </c>
-      <c r="T30" t="n">
-        <v>78</v>
-      </c>
-      <c r="U30" t="n">
-        <v>82</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>344</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/nest_issues_commented/MP_nest_data_issues_220825.xlsx
+++ b/data/nest_issues_commented/MP_nest_data_issues_220825.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t xml:space="preserve">season</t>
   </si>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">22102010</t>
   </si>
   <si>
-    <t xml:space="preserve">25112010</t>
+    <t xml:space="preserve">18112010</t>
   </si>
   <si>
     <t xml:space="preserve">not found</t>
@@ -246,114 +246,111 @@
     <t xml:space="preserve">1/3 adult size, fluffy</t>
   </si>
   <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heyfield Pair 2 (east side) Rye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Heyfield Pair 2 (east side) Rye_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19122010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22122010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Heyfield Pair 2 (east side) Rye_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Koonya West_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt Nepean Observatory Pt - The Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Pt Nepean Observatory Pt - The Steps_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21012011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03022011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Pt Nepean Observatory Pt - The Steps_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heyfield Pair 1 (west side) Rye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Heyfield Pair 1 (west side) Rye_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03102009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11102009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ropefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montforts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Montforts_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26112009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30112009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Montforts_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03012010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28012010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rye car park east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Rye car park east_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06022010</t>
+  </si>
+  <si>
     <t xml:space="preserve">34</t>
   </si>
   <si>
-    <t xml:space="preserve">Heyfield Pair 2 (east side) Rye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Heyfield Pair 2 (east side) Rye_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19122010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22122010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Heyfield Pair 2 (east side) Rye_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Koonya West_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt Nepean Observatory Pt - The Steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Pt Nepean Observatory Pt - The Steps_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21012011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03022011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201011_Pt Nepean Observatory Pt - The Steps_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05022011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heyfield Pair 1 (west side) Rye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Heyfield Pair 1 (west side) Rye_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03102009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18102009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ropefence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montforts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Montforts_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26112009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07122009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Montforts_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03012010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04022010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rye car park east</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200910_Rye car park east_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13022010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
     <t xml:space="preserve">St Andrews - Miami Drive West</t>
   </si>
   <si>
@@ -363,13 +360,13 @@
     <t xml:space="preserve">20012010</t>
   </si>
   <si>
-    <t xml:space="preserve">08022010</t>
+    <t xml:space="preserve">01022010</t>
   </si>
   <si>
     <t xml:space="preserve">signnest,ropefence</t>
   </si>
   <si>
-    <t xml:space="preserve">19</t>
+    <t xml:space="preserve">12</t>
   </si>
   <si>
     <t xml:space="preserve">St Andrews carpark west</t>
@@ -435,27 +432,30 @@
     <t xml:space="preserve">07012009</t>
   </si>
   <si>
+    <t xml:space="preserve">03022009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miami drive east access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Miami drive east access_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16102008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17102008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200809_Pt Nepean Observatory Pt - The Steps_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15012009</t>
+  </si>
+  <si>
     <t xml:space="preserve">10022009</t>
   </si>
   <si>
-    <t xml:space="preserve">Miami drive east access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Miami drive east access_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16102008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17102008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200809_Pt Nepean Observatory Pt - The Steps_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15012009</t>
-  </si>
-  <si>
     <t xml:space="preserve">St Andrews Boags Rocks</t>
   </si>
   <si>
@@ -477,13 +477,13 @@
     <t xml:space="preserve">15112007</t>
   </si>
   <si>
-    <t xml:space="preserve">12122007</t>
+    <t xml:space="preserve">05122007</t>
   </si>
   <si>
     <t xml:space="preserve">Adult size, mottled grey</t>
   </si>
   <si>
-    <t xml:space="preserve">27</t>
+    <t xml:space="preserve">20</t>
   </si>
   <si>
     <t xml:space="preserve">200607</t>
@@ -498,13 +498,16 @@
     <t xml:space="preserve">01092006</t>
   </si>
   <si>
-    <t xml:space="preserve">13062006</t>
+    <t xml:space="preserve">06062006</t>
   </si>
   <si>
     <t xml:space="preserve">-38 27.719</t>
   </si>
   <si>
     <t xml:space="preserve">144 52.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
   </si>
   <si>
     <t xml:space="preserve">200607_Heyfield Pair 2 (east side) Rye_1</t>
@@ -1024,7 +1027,7 @@
       </c>
       <c r="AB2"/>
       <c r="AC2" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AD2" t="s">
         <v>43</v>
@@ -1202,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AD4" t="s">
         <v>43</v>
@@ -1294,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AD5" t="s">
         <v>43</v>
@@ -1437,22 +1440,22 @@
         <v>76</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>40507</v>
+        <v>40500</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>40473</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>40507</v>
+        <v>40500</v>
       </c>
       <c r="S7" t="n">
         <v>110</v>
       </c>
       <c r="T7" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="U7" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1854,10 +1857,10 @@
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
@@ -1883,22 +1886,22 @@
         <v>76</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>40579</v>
+        <v>40572</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>40564</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>40579</v>
+        <v>40572</v>
       </c>
       <c r="S12" t="n">
         <v>201</v>
       </c>
       <c r="T12" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="U12" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1928,7 +1931,7 @@
         <v>43</v>
       </c>
       <c r="AE12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF12" t="s">
         <v>53</v>
@@ -1936,22 +1939,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
         <v>94</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>95</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>96</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>97</v>
       </c>
-      <c r="E13" t="s">
-        <v>98</v>
-      </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G13" t="s">
         <v>44</v>
@@ -1963,7 +1966,7 @@
         <v>39</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K13"/>
       <c r="L13"/>
@@ -1977,22 +1980,22 @@
         <v>76</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>40104</v>
+        <v>40097</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>40089</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>40104</v>
+        <v>40097</v>
       </c>
       <c r="S13" t="n">
         <v>91</v>
       </c>
       <c r="T13" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="U13" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2016,13 +2019,13 @@
         <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="AD13" t="s">
         <v>43</v>
       </c>
       <c r="AE13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF13" t="s">
         <v>53</v>
@@ -2030,22 +2033,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
         <v>100</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>101</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>102</v>
       </c>
-      <c r="E14" t="s">
-        <v>103</v>
-      </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G14" t="s">
         <v>44</v>
@@ -2071,22 +2074,22 @@
         <v>76</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>40154</v>
+        <v>40147</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>40143</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>40154</v>
+        <v>40147</v>
       </c>
       <c r="S14" t="n">
         <v>145</v>
       </c>
       <c r="T14" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="U14" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2110,13 +2113,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="AD14" t="s">
         <v>43</v>
       </c>
       <c r="AE14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AF14" t="s">
         <v>53</v>
@@ -2124,22 +2127,22 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" t="s">
         <v>105</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>106</v>
       </c>
-      <c r="E15" t="s">
-        <v>107</v>
-      </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G15" t="s">
         <v>44</v>
@@ -2165,22 +2168,22 @@
         <v>76</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>40213</v>
+        <v>40206</v>
       </c>
       <c r="Q15" s="1" t="n">
         <v>40181</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>40213</v>
+        <v>40206</v>
       </c>
       <c r="S15" t="n">
         <v>183</v>
       </c>
       <c r="T15" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="U15" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2204,13 +2207,13 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="AD15" t="s">
         <v>43</v>
       </c>
       <c r="AE15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AF15" t="s">
         <v>53</v>
@@ -2218,22 +2221,22 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
         <v>109</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
         <v>110</v>
       </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>111</v>
-      </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G16" t="s">
         <v>44</v>
@@ -2259,22 +2262,22 @@
         <v>76</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>40222</v>
+        <v>40215</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>40187</v>
+        <v>40181</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>40222</v>
+        <v>40215</v>
       </c>
       <c r="S16" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="T16" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="U16" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2298,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="AD16" t="s">
         <v>43</v>
       </c>
       <c r="AE16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF16" t="s">
         <v>53</v>
@@ -2312,22 +2315,22 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" t="s">
         <v>113</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>114</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>115</v>
       </c>
-      <c r="E17" t="s">
-        <v>116</v>
-      </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" t="s">
         <v>44</v>
@@ -2339,7 +2342,7 @@
         <v>39</v>
       </c>
       <c r="J17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K17"/>
       <c r="L17"/>
@@ -2353,22 +2356,22 @@
         <v>76</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>40217</v>
+        <v>40210</v>
       </c>
       <c r="Q17" s="1" t="n">
         <v>40198</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>40217</v>
+        <v>40210</v>
       </c>
       <c r="S17" t="n">
         <v>200</v>
       </c>
       <c r="T17" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="U17" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2392,13 +2395,13 @@
         <v>3</v>
       </c>
       <c r="AC17" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="AD17" t="s">
         <v>43</v>
       </c>
       <c r="AE17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s">
         <v>53</v>
@@ -2406,22 +2409,22 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
         <v>119</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>120</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
         <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" t="s">
-        <v>122</v>
       </c>
       <c r="G18" t="s">
         <v>37</v>
@@ -2433,7 +2436,7 @@
         <v>39</v>
       </c>
       <c r="J18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K18"/>
       <c r="L18"/>
@@ -2480,7 +2483,7 @@
         <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="AD18" t="s">
         <v>43</v>
@@ -2494,22 +2497,22 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" t="s">
         <v>123</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>124</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>125</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" t="s">
         <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" t="s">
-        <v>127</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -2584,22 +2587,22 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" t="s">
         <v>128</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>129</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" t="s">
         <v>130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" t="s">
-        <v>131</v>
       </c>
       <c r="G20" t="s">
         <v>37</v>
@@ -2672,22 +2675,22 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
         <v>132</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>133</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" t="s">
         <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
       </c>
       <c r="G21" t="s">
         <v>37</v>
@@ -2762,22 +2765,22 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" t="s">
         <v>136</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" t="s">
-        <v>135</v>
-      </c>
-      <c r="F22" t="s">
-        <v>137</v>
       </c>
       <c r="G22" t="s">
         <v>37</v>
@@ -2852,22 +2855,22 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" t="s">
         <v>138</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>139</v>
       </c>
-      <c r="E23" t="s">
-        <v>140</v>
-      </c>
       <c r="F23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G23" t="s">
         <v>44</v>
@@ -2879,7 +2882,7 @@
         <v>39</v>
       </c>
       <c r="J23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K23"/>
       <c r="L23"/>
@@ -2893,22 +2896,22 @@
         <v>76</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>39854</v>
+        <v>39847</v>
       </c>
       <c r="Q23" s="1" t="n">
         <v>39820</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>39854</v>
+        <v>39847</v>
       </c>
       <c r="S23" t="n">
         <v>187</v>
       </c>
       <c r="T23" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="U23" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2946,22 +2949,22 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
         <v>141</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>142</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" t="s">
         <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" t="s">
-        <v>144</v>
       </c>
       <c r="G24" t="s">
         <v>37</v>
@@ -3034,22 +3037,22 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
       </c>
       <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
         <v>145</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" t="s">
         <v>146</v>
-      </c>
-      <c r="E25" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" t="s">
-        <v>140</v>
       </c>
       <c r="G25" t="s">
         <v>37</v>
@@ -3061,7 +3064,7 @@
         <v>39</v>
       </c>
       <c r="J25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K25"/>
       <c r="L25"/>
@@ -3124,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
         <v>147</v>
@@ -3253,22 +3256,22 @@
         <v>155</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>39428</v>
+        <v>39421</v>
       </c>
       <c r="Q27" s="1" t="n">
         <v>39401</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>39428</v>
+        <v>39421</v>
       </c>
       <c r="S27" t="n">
         <v>134</v>
       </c>
       <c r="T27" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="U27" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3292,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AD27" t="s">
         <v>43</v>
@@ -3351,22 +3354,22 @@
         <v>76</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>38881</v>
+        <v>38874</v>
       </c>
       <c r="Q28" s="1" t="n">
         <v>38846</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>38881</v>
+        <v>38874</v>
       </c>
       <c r="S28" t="n">
         <v>309</v>
       </c>
       <c r="T28" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="U28" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3390,13 +3393,13 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="AD28" t="s">
         <v>43</v>
       </c>
       <c r="AE28" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="AF28" t="s">
         <v>53</v>
@@ -3410,16 +3413,16 @@
         <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G29" t="s">
         <v>37</v>
@@ -3478,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="AD29" t="s">
         <v>43</v>
